--- a/public/Export/Exportar_Copiapo_PM.xlsx
+++ b/public/Export/Exportar_Copiapo_PM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernando/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D083840-EF02-FD44-B7B5-447AAC7AEF0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9970288E-A676-7245-9C73-3107C70C8DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="19420" windowHeight="10420" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="30080" windowHeight="16920" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Utilidad" sheetId="1" state="hidden" r:id="rId1"/>
@@ -1982,51 +1982,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="10" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="10" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="10" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="10" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="10" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="15" fillId="10" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="15" fillId="10" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2050,6 +2005,9 @@
     </xf>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="12" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2080,6 +2038,48 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="37" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="10" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="10" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="10" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="10" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="10" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="15" fillId="10" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="15" fillId="10" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -10887,11 +10887,11 @@
         <v>0</v>
       </c>
       <c r="P68" s="145">
-        <f>IF(D1&gt;1,D1/100,D1)</f>
+        <f>D1/100</f>
         <v>0</v>
       </c>
       <c r="Q68" s="145">
-        <f>IF(F1&gt;1,F1/100,F1)</f>
+        <f>F1/100</f>
         <v>0</v>
       </c>
       <c r="R68" s="140">
@@ -10944,11 +10944,11 @@
         <v>0</v>
       </c>
       <c r="P69" s="145">
-        <f t="shared" ref="P69:P129" si="3">IF(D2&gt;1,D2/100,D2)</f>
+        <f t="shared" ref="P69:P129" si="3">D2/100</f>
         <v>0</v>
       </c>
       <c r="Q69" s="145">
-        <f t="shared" ref="Q69:Q129" si="4">IF(F2&gt;1,F2/100,F2)</f>
+        <f t="shared" ref="Q69:Q129" si="4">F2/100</f>
         <v>0</v>
       </c>
       <c r="R69" s="140">
@@ -13452,7 +13452,7 @@
         <v>6.3589100652000005E-2</v>
       </c>
       <c r="Q108" s="145">
-        <f>IF(F41&gt;0.1,F41/100,F41)</f>
+        <f t="shared" si="4"/>
         <v>5.3045604898999997E-3</v>
       </c>
       <c r="R108" s="140">
@@ -13594,7 +13594,7 @@
         <v>7.6110318891999998E-2</v>
       </c>
       <c r="Q110" s="145">
-        <f>IF(F43&gt;0.1,F43/100,F43)</f>
+        <f t="shared" si="4"/>
         <v>1.2332926971E-2</v>
       </c>
       <c r="R110" s="140">
@@ -13879,7 +13879,7 @@
         <v>5.2359999999999997E-2</v>
       </c>
       <c r="Q115" s="145">
-        <f>IF(F48&gt;0.1,F48/100,F48)</f>
+        <f t="shared" si="4"/>
         <v>4.7169736407000002E-3</v>
       </c>
       <c r="R115" s="140">
@@ -38841,79 +38841,79 @@
     </row>
     <row r="2" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="112"/>
-      <c r="B2" s="186"/>
-      <c r="C2" s="187"/>
-      <c r="D2" s="188" t="s">
+      <c r="B2" s="209"/>
+      <c r="C2" s="210"/>
+      <c r="D2" s="211" t="s">
         <v>124</v>
       </c>
-      <c r="E2" s="189"/>
-      <c r="F2" s="189"/>
-      <c r="G2" s="189"/>
-      <c r="H2" s="189"/>
-      <c r="I2" s="189"/>
-      <c r="J2" s="189"/>
-      <c r="K2" s="189"/>
-      <c r="L2" s="189"/>
-      <c r="M2" s="189"/>
+      <c r="E2" s="212"/>
+      <c r="F2" s="212"/>
+      <c r="G2" s="212"/>
+      <c r="H2" s="212"/>
+      <c r="I2" s="212"/>
+      <c r="J2" s="212"/>
+      <c r="K2" s="212"/>
+      <c r="L2" s="212"/>
+      <c r="M2" s="212"/>
       <c r="N2" s="102"/>
       <c r="O2" s="89"/>
       <c r="P2" s="102"/>
     </row>
     <row r="3" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="112"/>
-      <c r="B3" s="186"/>
-      <c r="C3" s="187"/>
-      <c r="D3" s="190"/>
-      <c r="E3" s="191"/>
-      <c r="F3" s="191"/>
-      <c r="G3" s="191"/>
-      <c r="H3" s="191"/>
-      <c r="I3" s="191"/>
-      <c r="J3" s="191"/>
-      <c r="K3" s="191"/>
-      <c r="L3" s="191"/>
-      <c r="M3" s="191"/>
+      <c r="B3" s="209"/>
+      <c r="C3" s="210"/>
+      <c r="D3" s="213"/>
+      <c r="E3" s="214"/>
+      <c r="F3" s="214"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="214"/>
+      <c r="I3" s="214"/>
+      <c r="J3" s="214"/>
+      <c r="K3" s="214"/>
+      <c r="L3" s="214"/>
+      <c r="M3" s="214"/>
       <c r="N3" s="102"/>
       <c r="O3" s="89"/>
       <c r="P3" s="102"/>
     </row>
     <row r="4" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="112"/>
-      <c r="B4" s="186"/>
-      <c r="C4" s="186"/>
-      <c r="D4" s="192" t="s">
+      <c r="B4" s="209"/>
+      <c r="C4" s="209"/>
+      <c r="D4" s="215" t="s">
         <v>125</v>
       </c>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="192"/>
-      <c r="K4" s="192"/>
-      <c r="L4" s="194">
+      <c r="E4" s="215"/>
+      <c r="F4" s="215"/>
+      <c r="G4" s="215"/>
+      <c r="H4" s="215"/>
+      <c r="I4" s="215"/>
+      <c r="J4" s="215"/>
+      <c r="K4" s="215"/>
+      <c r="L4" s="217">
         <f ca="1">TODAY()-3</f>
-        <v>45594</v>
-      </c>
-      <c r="M4" s="194"/>
+        <v>45622</v>
+      </c>
+      <c r="M4" s="217"/>
       <c r="N4" s="102"/>
       <c r="O4" s="89"/>
       <c r="P4" s="102"/>
     </row>
     <row r="5" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="112"/>
-      <c r="B5" s="186"/>
-      <c r="C5" s="186"/>
-      <c r="D5" s="193"/>
-      <c r="E5" s="193"/>
-      <c r="F5" s="193"/>
-      <c r="G5" s="193"/>
-      <c r="H5" s="193"/>
-      <c r="I5" s="193"/>
-      <c r="J5" s="193"/>
-      <c r="K5" s="193"/>
-      <c r="L5" s="195"/>
-      <c r="M5" s="195"/>
+      <c r="B5" s="209"/>
+      <c r="C5" s="209"/>
+      <c r="D5" s="216"/>
+      <c r="E5" s="216"/>
+      <c r="F5" s="216"/>
+      <c r="G5" s="216"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="216"/>
+      <c r="K5" s="216"/>
+      <c r="L5" s="218"/>
+      <c r="M5" s="218"/>
       <c r="N5" s="102"/>
       <c r="O5" s="89"/>
       <c r="P5" s="102"/>
@@ -38938,9 +38938,9 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="113"/>
-      <c r="B7" s="197"/>
-      <c r="C7" s="197"/>
-      <c r="D7" s="197"/>
+      <c r="B7" s="207"/>
+      <c r="C7" s="207"/>
+      <c r="D7" s="207"/>
       <c r="E7" s="125" t="s">
         <v>126</v>
       </c>
@@ -38953,8 +38953,8 @@
       <c r="H7" s="125" t="s">
         <v>127</v>
       </c>
-      <c r="I7" s="197"/>
-      <c r="J7" s="197"/>
+      <c r="I7" s="207"/>
+      <c r="J7" s="207"/>
       <c r="K7" s="125" t="s">
         <v>126</v>
       </c>
@@ -38972,9 +38972,9 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="113"/>
-      <c r="B8" s="197"/>
-      <c r="C8" s="197"/>
-      <c r="D8" s="197"/>
+      <c r="B8" s="207"/>
+      <c r="C8" s="207"/>
+      <c r="D8" s="207"/>
       <c r="E8" s="125" t="s">
         <v>1</v>
       </c>
@@ -38987,8 +38987,8 @@
       <c r="H8" s="125" t="s">
         <v>131</v>
       </c>
-      <c r="I8" s="197"/>
-      <c r="J8" s="197"/>
+      <c r="I8" s="207"/>
+      <c r="J8" s="207"/>
       <c r="K8" s="125" t="s">
         <v>1</v>
       </c>
@@ -39006,33 +39006,33 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="113"/>
-      <c r="B9" s="198" t="s">
+      <c r="B9" s="194" t="s">
         <v>75</v>
       </c>
-      <c r="C9" s="198"/>
-      <c r="D9" s="198"/>
-      <c r="E9" s="198"/>
-      <c r="F9" s="198"/>
-      <c r="G9" s="198"/>
-      <c r="H9" s="198" t="s">
+      <c r="C9" s="194"/>
+      <c r="D9" s="194"/>
+      <c r="E9" s="194"/>
+      <c r="F9" s="194"/>
+      <c r="G9" s="194"/>
+      <c r="H9" s="194" t="s">
         <v>132</v>
       </c>
-      <c r="I9" s="198"/>
-      <c r="J9" s="198"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="198"/>
+      <c r="I9" s="194"/>
+      <c r="J9" s="194"/>
+      <c r="K9" s="194"/>
+      <c r="L9" s="194"/>
+      <c r="M9" s="194"/>
+      <c r="N9" s="194"/>
       <c r="O9" s="89"/>
       <c r="P9" s="102"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="113"/>
-      <c r="B10" s="199" t="s">
+      <c r="B10" s="205" t="s">
         <v>133</v>
       </c>
-      <c r="C10" s="199"/>
-      <c r="D10" s="199"/>
+      <c r="C10" s="205"/>
+      <c r="D10" s="205"/>
       <c r="E10" s="126">
         <f>Flujos!H43</f>
         <v>987340</v>
@@ -39074,11 +39074,11 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="113"/>
-      <c r="B11" s="199" t="s">
+      <c r="B11" s="205" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="199"/>
-      <c r="D11" s="199"/>
+      <c r="C11" s="205"/>
+      <c r="D11" s="205"/>
       <c r="E11" s="91"/>
       <c r="F11" s="90"/>
       <c r="G11" s="95"/>
@@ -39108,11 +39108,11 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="118"/>
-      <c r="B12" s="200" t="s">
+      <c r="B12" s="208" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="200"/>
-      <c r="D12" s="200"/>
+      <c r="C12" s="208"/>
+      <c r="D12" s="208"/>
       <c r="E12" s="91">
         <f>Utilidad!O76</f>
         <v>2628.4124999999999</v>
@@ -39140,11 +39140,11 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="118"/>
-      <c r="B13" s="200" t="s">
+      <c r="B13" s="208" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="200"/>
-      <c r="D13" s="200"/>
+      <c r="C13" s="208"/>
+      <c r="D13" s="208"/>
       <c r="E13" s="91"/>
       <c r="F13" s="92"/>
       <c r="G13" s="95"/>
@@ -39160,11 +39160,11 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="118"/>
-      <c r="B14" s="200" t="s">
+      <c r="B14" s="208" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="200"/>
-      <c r="D14" s="200"/>
+      <c r="C14" s="208"/>
+      <c r="D14" s="208"/>
       <c r="E14" s="91"/>
       <c r="F14" s="92"/>
       <c r="G14" s="95"/>
@@ -39180,11 +39180,11 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="118"/>
-      <c r="B15" s="200" t="s">
+      <c r="B15" s="208" t="s">
         <v>146</v>
       </c>
-      <c r="C15" s="200"/>
-      <c r="D15" s="200"/>
+      <c r="C15" s="208"/>
+      <c r="D15" s="208"/>
       <c r="E15" s="91">
         <f>Utilidad!O85</f>
         <v>683.28750000000002</v>
@@ -39212,11 +39212,11 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="118"/>
-      <c r="B16" s="200" t="s">
+      <c r="B16" s="208" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="200"/>
-      <c r="D16" s="200"/>
+      <c r="C16" s="208"/>
+      <c r="D16" s="208"/>
       <c r="E16" s="91"/>
       <c r="F16" s="92"/>
       <c r="G16" s="95"/>
@@ -39232,11 +39232,11 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="118"/>
-      <c r="B17" s="200" t="s">
+      <c r="B17" s="208" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="200"/>
-      <c r="D17" s="200"/>
+      <c r="C17" s="208"/>
+      <c r="D17" s="208"/>
       <c r="E17" s="91"/>
       <c r="F17" s="92"/>
       <c r="G17" s="95"/>
@@ -39252,11 +39252,11 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="118"/>
-      <c r="B18" s="200" t="s">
+      <c r="B18" s="208" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="200"/>
-      <c r="D18" s="200"/>
+      <c r="C18" s="208"/>
+      <c r="D18" s="208"/>
       <c r="E18" s="91">
         <f>Utilidad!O73</f>
         <v>290.27249999999998</v>
@@ -39284,11 +39284,11 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="118"/>
-      <c r="B19" s="200" t="s">
+      <c r="B19" s="208" t="s">
         <v>135</v>
       </c>
-      <c r="C19" s="200"/>
-      <c r="D19" s="200"/>
+      <c r="C19" s="208"/>
+      <c r="D19" s="208"/>
       <c r="E19" s="91"/>
       <c r="F19" s="92"/>
       <c r="G19" s="95"/>
@@ -39304,11 +39304,11 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="118"/>
-      <c r="B20" s="200" t="s">
+      <c r="B20" s="208" t="s">
         <v>136</v>
       </c>
-      <c r="C20" s="200"/>
-      <c r="D20" s="200"/>
+      <c r="C20" s="208"/>
+      <c r="D20" s="208"/>
       <c r="E20" s="91"/>
       <c r="F20" s="92"/>
       <c r="G20" s="95"/>
@@ -39324,11 +39324,11 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" s="118"/>
-      <c r="B21" s="200" t="s">
+      <c r="B21" s="208" t="s">
         <v>137</v>
       </c>
-      <c r="C21" s="200"/>
-      <c r="D21" s="200"/>
+      <c r="C21" s="208"/>
+      <c r="D21" s="208"/>
       <c r="E21" s="91"/>
       <c r="F21" s="92"/>
       <c r="G21" s="95"/>
@@ -39344,11 +39344,11 @@
     </row>
     <row r="22" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="118"/>
-      <c r="B22" s="196" t="s">
+      <c r="B22" s="206" t="s">
         <v>138</v>
       </c>
-      <c r="C22" s="196"/>
-      <c r="D22" s="196"/>
+      <c r="C22" s="206"/>
+      <c r="D22" s="206"/>
       <c r="E22" s="98"/>
       <c r="F22" s="128"/>
       <c r="G22" s="129"/>
@@ -39364,11 +39364,11 @@
     </row>
     <row r="23" spans="1:16" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="113"/>
-      <c r="B23" s="217" t="s">
+      <c r="B23" s="203" t="s">
         <v>139</v>
       </c>
-      <c r="C23" s="217"/>
-      <c r="D23" s="217"/>
+      <c r="C23" s="203"/>
+      <c r="D23" s="203"/>
       <c r="E23" s="97">
         <f>SUM(E10:E22)</f>
         <v>990941.97249999992</v>
@@ -39396,33 +39396,33 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" s="113"/>
-      <c r="B24" s="218" t="s">
+      <c r="B24" s="204" t="s">
         <v>140</v>
       </c>
-      <c r="C24" s="218"/>
-      <c r="D24" s="218"/>
-      <c r="E24" s="218"/>
-      <c r="F24" s="218"/>
-      <c r="G24" s="218"/>
-      <c r="H24" s="218" t="s">
+      <c r="C24" s="204"/>
+      <c r="D24" s="204"/>
+      <c r="E24" s="204"/>
+      <c r="F24" s="204"/>
+      <c r="G24" s="204"/>
+      <c r="H24" s="204" t="s">
         <v>141</v>
       </c>
-      <c r="I24" s="218"/>
-      <c r="J24" s="218"/>
-      <c r="K24" s="218"/>
-      <c r="L24" s="218"/>
-      <c r="M24" s="218"/>
+      <c r="I24" s="204"/>
+      <c r="J24" s="204"/>
+      <c r="K24" s="204"/>
+      <c r="L24" s="204"/>
+      <c r="M24" s="204"/>
       <c r="N24" s="102"/>
       <c r="O24" s="89"/>
       <c r="P24" s="102"/>
     </row>
     <row r="25" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="113"/>
-      <c r="B25" s="199" t="s">
+      <c r="B25" s="205" t="s">
         <v>122</v>
       </c>
-      <c r="C25" s="199"/>
-      <c r="D25" s="199"/>
+      <c r="C25" s="205"/>
+      <c r="D25" s="205"/>
       <c r="E25" s="91">
         <f>'Datos Extra'!B1</f>
         <v>45971</v>
@@ -39435,11 +39435,11 @@
         <f>+E25*F25</f>
         <v>30156.976000000002</v>
       </c>
-      <c r="H25" s="199" t="s">
+      <c r="H25" s="205" t="s">
         <v>133</v>
       </c>
-      <c r="I25" s="199"/>
-      <c r="J25" s="199"/>
+      <c r="I25" s="205"/>
+      <c r="J25" s="205"/>
       <c r="K25" s="99">
         <f>Flujos!H62</f>
         <v>894372.97250000003</v>
@@ -39458,11 +39458,11 @@
     </row>
     <row r="26" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="113"/>
-      <c r="B26" s="209" t="s">
+      <c r="B26" s="195" t="s">
         <v>139</v>
       </c>
-      <c r="C26" s="209"/>
-      <c r="D26" s="209"/>
+      <c r="C26" s="195"/>
+      <c r="D26" s="195"/>
       <c r="E26" s="105">
         <f>SUM(E24:E25)</f>
         <v>45971</v>
@@ -39475,11 +39475,11 @@
         <f>SUM(G24:G25)</f>
         <v>30156.976000000002</v>
       </c>
-      <c r="H26" s="209" t="s">
+      <c r="H26" s="195" t="s">
         <v>139</v>
       </c>
-      <c r="I26" s="209"/>
-      <c r="J26" s="209"/>
+      <c r="I26" s="195"/>
+      <c r="J26" s="195"/>
       <c r="K26" s="108">
         <f>K25</f>
         <v>894372.97250000003</v>
@@ -39516,20 +39516,20 @@
     </row>
     <row r="28" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="113"/>
-      <c r="B28" s="210" t="s">
+      <c r="B28" s="196" t="s">
         <v>142</v>
       </c>
-      <c r="C28" s="210"/>
-      <c r="D28" s="210"/>
-      <c r="E28" s="210"/>
-      <c r="F28" s="210"/>
-      <c r="G28" s="210"/>
-      <c r="H28" s="210"/>
-      <c r="I28" s="210"/>
-      <c r="J28" s="210"/>
-      <c r="K28" s="210"/>
-      <c r="L28" s="210"/>
-      <c r="M28" s="210"/>
+      <c r="C28" s="196"/>
+      <c r="D28" s="196"/>
+      <c r="E28" s="196"/>
+      <c r="F28" s="196"/>
+      <c r="G28" s="196"/>
+      <c r="H28" s="196"/>
+      <c r="I28" s="196"/>
+      <c r="J28" s="196"/>
+      <c r="K28" s="196"/>
+      <c r="L28" s="196"/>
+      <c r="M28" s="196"/>
       <c r="N28" s="102"/>
       <c r="O28" s="89"/>
       <c r="P28" s="102"/>
@@ -39554,69 +39554,69 @@
     </row>
     <row r="30" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="113"/>
-      <c r="B30" s="211" t="s">
+      <c r="B30" s="197" t="s">
         <v>143</v>
       </c>
-      <c r="C30" s="212"/>
-      <c r="D30" s="213"/>
+      <c r="C30" s="198"/>
+      <c r="D30" s="199"/>
       <c r="E30" s="102"/>
       <c r="F30" s="102"/>
-      <c r="G30" s="214" t="s">
+      <c r="G30" s="200" t="s">
         <v>144</v>
       </c>
-      <c r="H30" s="215"/>
-      <c r="I30" s="216"/>
+      <c r="H30" s="201"/>
+      <c r="I30" s="202"/>
       <c r="J30" s="102"/>
-      <c r="K30" s="211" t="s">
+      <c r="K30" s="197" t="s">
         <v>145</v>
       </c>
-      <c r="L30" s="212"/>
-      <c r="M30" s="213"/>
+      <c r="L30" s="198"/>
+      <c r="M30" s="199"/>
       <c r="N30" s="102"/>
       <c r="O30" s="89"/>
       <c r="P30" s="102"/>
     </row>
     <row r="31" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="131"/>
-      <c r="B31" s="201">
+      <c r="B31" s="186">
         <f>Flujos!J74/100</f>
         <v>8.689760048611872E-2</v>
       </c>
-      <c r="C31" s="201"/>
-      <c r="D31" s="201"/>
+      <c r="C31" s="186"/>
+      <c r="D31" s="186"/>
       <c r="E31" s="102"/>
       <c r="F31" s="102"/>
-      <c r="G31" s="202">
+      <c r="G31" s="187">
         <f>Utilidad!I94</f>
         <v>0.39527507192083183</v>
       </c>
-      <c r="H31" s="202"/>
-      <c r="I31" s="202"/>
+      <c r="H31" s="187"/>
+      <c r="I31" s="187"/>
       <c r="J31" s="102"/>
-      <c r="K31" s="203">
+      <c r="K31" s="188">
         <f>Utilidad!I104</f>
         <v>0.60160918139617092</v>
       </c>
-      <c r="L31" s="204"/>
-      <c r="M31" s="205"/>
+      <c r="L31" s="189"/>
+      <c r="M31" s="190"/>
       <c r="N31" s="102"/>
       <c r="O31" s="89"/>
       <c r="P31" s="102"/>
     </row>
     <row r="32" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14"/>
-      <c r="B32" s="202"/>
-      <c r="C32" s="202"/>
-      <c r="D32" s="202"/>
+      <c r="B32" s="187"/>
+      <c r="C32" s="187"/>
+      <c r="D32" s="187"/>
       <c r="E32" s="102"/>
       <c r="F32" s="102"/>
-      <c r="G32" s="202"/>
-      <c r="H32" s="202"/>
-      <c r="I32" s="202"/>
+      <c r="G32" s="187"/>
+      <c r="H32" s="187"/>
+      <c r="I32" s="187"/>
       <c r="J32" s="102"/>
-      <c r="K32" s="206"/>
-      <c r="L32" s="207"/>
-      <c r="M32" s="208"/>
+      <c r="K32" s="191"/>
+      <c r="L32" s="192"/>
+      <c r="M32" s="193"/>
       <c r="O32" s="89"/>
     </row>
     <row r="33" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -39693,6 +39693,26 @@
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="B2:C5"/>
+    <mergeCell ref="D2:M3"/>
+    <mergeCell ref="D4:I5"/>
+    <mergeCell ref="J4:K5"/>
+    <mergeCell ref="L4:M5"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B7:D8"/>
+    <mergeCell ref="I7:J8"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
     <mergeCell ref="B31:D32"/>
     <mergeCell ref="G31:I32"/>
     <mergeCell ref="K31:M32"/>
@@ -39709,26 +39729,6 @@
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="H25:J25"/>
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B7:D8"/>
-    <mergeCell ref="I7:J8"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B2:C5"/>
-    <mergeCell ref="D2:M3"/>
-    <mergeCell ref="D4:I5"/>
-    <mergeCell ref="J4:K5"/>
-    <mergeCell ref="L4:M5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup scale="85" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/public/Export/Exportar_Copiapo_PM.xlsx
+++ b/public/Export/Exportar_Copiapo_PM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernando/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernando/Documents/GitHub/minera/public/Export/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B255B67-06EB-FB4E-AD43-FABC956187E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2730C7-FF8B-0E42-8A48-8EAB4C847B25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="26300" windowHeight="15800" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Utilidad" sheetId="1" r:id="rId1"/>
@@ -1665,7 +1665,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="235">
+  <cellXfs count="230">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2072,6 +2072,12 @@
     <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="0" fillId="13" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2098,6 +2104,75 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="29" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="24" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="21" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="32" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="33" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="34" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="37" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2129,94 +2204,6 @@
     <xf numFmtId="170" fontId="15" fillId="10" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="29" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="24" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="21" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="32" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="33" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="34" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="37" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="0" fillId="13" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
@@ -10883,17 +10870,17 @@
       <c r="I66" s="134"/>
       <c r="J66" s="134"/>
       <c r="K66" s="134"/>
-      <c r="L66" s="186"/>
-      <c r="M66" s="186"/>
+      <c r="L66" s="192"/>
+      <c r="M66" s="192"/>
       <c r="N66" s="134"/>
-      <c r="O66" s="187" t="s">
-        <v>0</v>
-      </c>
-      <c r="P66" s="187"/>
-      <c r="Q66" s="187"/>
+      <c r="O66" s="193" t="s">
+        <v>0</v>
+      </c>
+      <c r="P66" s="193"/>
+      <c r="Q66" s="193"/>
       <c r="R66" s="134"/>
-      <c r="S66" s="188"/>
-      <c r="T66" s="188"/>
+      <c r="S66" s="194"/>
+      <c r="T66" s="194"/>
       <c r="U66" s="133"/>
       <c r="V66" s="133"/>
       <c r="W66" s="156"/>
@@ -10901,10 +10888,10 @@
       <c r="Y66" s="133"/>
       <c r="Z66" s="133"/>
       <c r="AA66" s="133"/>
-      <c r="AB66" s="182"/>
-      <c r="AC66" s="182"/>
-      <c r="AD66" s="182"/>
-      <c r="AE66" s="182"/>
+      <c r="AB66" s="188"/>
+      <c r="AC66" s="188"/>
+      <c r="AD66" s="188"/>
+      <c r="AE66" s="188"/>
       <c r="AF66" s="133"/>
       <c r="AG66" s="133"/>
       <c r="AH66" s="133"/>
@@ -14583,8 +14570,8 @@
       <c r="I126" s="134"/>
       <c r="J126" s="134"/>
       <c r="K126" s="169"/>
-      <c r="L126" s="183"/>
-      <c r="M126" s="183"/>
+      <c r="L126" s="189"/>
+      <c r="M126" s="189"/>
       <c r="N126" s="134" t="s">
         <v>67</v>
       </c>
@@ -14661,9 +14648,9 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="S127" s="184"/>
-      <c r="T127" s="184"/>
-      <c r="U127" s="184"/>
+      <c r="S127" s="190"/>
+      <c r="T127" s="190"/>
+      <c r="U127" s="190"/>
       <c r="V127" s="133"/>
       <c r="W127" s="133"/>
       <c r="X127" s="133"/>
@@ -16736,8 +16723,8 @@
       <c r="I177" s="133"/>
       <c r="J177" s="133"/>
       <c r="K177" s="156"/>
-      <c r="L177" s="185"/>
-      <c r="M177" s="185"/>
+      <c r="L177" s="191"/>
+      <c r="M177" s="191"/>
       <c r="N177" s="133"/>
       <c r="S177" s="133"/>
       <c r="T177" s="133"/>
@@ -34612,23 +34599,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="189" t="s">
+      <c r="B2" s="195" t="s">
         <v>94</v>
       </c>
-      <c r="C2" s="189"/>
-      <c r="D2" s="189"/>
-      <c r="E2" s="189"/>
-      <c r="G2" s="189" t="s">
+      <c r="C2" s="195"/>
+      <c r="D2" s="195"/>
+      <c r="E2" s="195"/>
+      <c r="G2" s="195" t="s">
         <v>95</v>
       </c>
-      <c r="H2" s="189"/>
-      <c r="I2" s="189"/>
-      <c r="J2" s="189"/>
-      <c r="L2" s="190" t="s">
+      <c r="H2" s="195"/>
+      <c r="I2" s="195"/>
+      <c r="J2" s="195"/>
+      <c r="L2" s="196" t="s">
         <v>96</v>
       </c>
-      <c r="M2" s="190"/>
-      <c r="N2" s="190"/>
+      <c r="M2" s="196"/>
+      <c r="N2" s="196"/>
       <c r="P2" s="54" t="s">
         <v>97</v>
       </c>
@@ -38924,7 +38911,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:R40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.1640625" customWidth="1"/>
@@ -38941,11 +38928,11 @@
     <col min="14" max="14" width="10.33203125" customWidth="1"/>
     <col min="15" max="15" width="3.33203125" customWidth="1"/>
     <col min="16" max="16" width="3.6640625" customWidth="1"/>
-    <col min="17" max="17" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22" customWidth="1"/>
     <col min="18" max="18" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="111"/>
       <c r="B1" s="87"/>
       <c r="C1" s="87"/>
@@ -38963,86 +38950,86 @@
       <c r="O1" s="88"/>
       <c r="P1" s="110"/>
     </row>
-    <row r="2" spans="1:19" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="112"/>
-      <c r="B2" s="191"/>
-      <c r="C2" s="192"/>
-      <c r="D2" s="193" t="s">
+      <c r="B2" s="220"/>
+      <c r="C2" s="221"/>
+      <c r="D2" s="222" t="s">
         <v>124</v>
       </c>
-      <c r="E2" s="194"/>
-      <c r="F2" s="194"/>
-      <c r="G2" s="194"/>
-      <c r="H2" s="194"/>
-      <c r="I2" s="194"/>
-      <c r="J2" s="194"/>
-      <c r="K2" s="194"/>
-      <c r="L2" s="194"/>
-      <c r="M2" s="194"/>
+      <c r="E2" s="223"/>
+      <c r="F2" s="223"/>
+      <c r="G2" s="223"/>
+      <c r="H2" s="223"/>
+      <c r="I2" s="223"/>
+      <c r="J2" s="223"/>
+      <c r="K2" s="223"/>
+      <c r="L2" s="223"/>
+      <c r="M2" s="223"/>
       <c r="N2" s="102"/>
       <c r="O2" s="89"/>
       <c r="P2" s="102"/>
     </row>
-    <row r="3" spans="1:19" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="112"/>
-      <c r="B3" s="191"/>
-      <c r="C3" s="192"/>
-      <c r="D3" s="195"/>
-      <c r="E3" s="196"/>
-      <c r="F3" s="196"/>
-      <c r="G3" s="196"/>
-      <c r="H3" s="196"/>
-      <c r="I3" s="196"/>
-      <c r="J3" s="196"/>
-      <c r="K3" s="196"/>
-      <c r="L3" s="196"/>
-      <c r="M3" s="196"/>
+      <c r="B3" s="220"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="224"/>
+      <c r="E3" s="225"/>
+      <c r="F3" s="225"/>
+      <c r="G3" s="225"/>
+      <c r="H3" s="225"/>
+      <c r="I3" s="225"/>
+      <c r="J3" s="225"/>
+      <c r="K3" s="225"/>
+      <c r="L3" s="225"/>
+      <c r="M3" s="225"/>
       <c r="N3" s="102"/>
       <c r="O3" s="89"/>
       <c r="P3" s="102"/>
     </row>
-    <row r="4" spans="1:19" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="112"/>
-      <c r="B4" s="191"/>
-      <c r="C4" s="191"/>
-      <c r="D4" s="197" t="s">
+      <c r="B4" s="220"/>
+      <c r="C4" s="220"/>
+      <c r="D4" s="226" t="s">
         <v>125</v>
       </c>
-      <c r="E4" s="197"/>
-      <c r="F4" s="197"/>
-      <c r="G4" s="197"/>
-      <c r="H4" s="197"/>
-      <c r="I4" s="197"/>
-      <c r="J4" s="197"/>
-      <c r="K4" s="197"/>
-      <c r="L4" s="199">
+      <c r="E4" s="226"/>
+      <c r="F4" s="226"/>
+      <c r="G4" s="226"/>
+      <c r="H4" s="226"/>
+      <c r="I4" s="226"/>
+      <c r="J4" s="226"/>
+      <c r="K4" s="226"/>
+      <c r="L4" s="228">
         <f ca="1">TODAY()-4</f>
-        <v>45892</v>
-      </c>
-      <c r="M4" s="199"/>
+        <v>45893</v>
+      </c>
+      <c r="M4" s="228"/>
       <c r="N4" s="102"/>
       <c r="O4" s="89"/>
       <c r="P4" s="102"/>
     </row>
-    <row r="5" spans="1:19" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="112"/>
-      <c r="B5" s="191"/>
-      <c r="C5" s="191"/>
-      <c r="D5" s="198"/>
-      <c r="E5" s="198"/>
-      <c r="F5" s="198"/>
-      <c r="G5" s="198"/>
-      <c r="H5" s="198"/>
-      <c r="I5" s="198"/>
-      <c r="J5" s="198"/>
-      <c r="K5" s="198"/>
-      <c r="L5" s="200"/>
-      <c r="M5" s="200"/>
+      <c r="B5" s="220"/>
+      <c r="C5" s="220"/>
+      <c r="D5" s="227"/>
+      <c r="E5" s="227"/>
+      <c r="F5" s="227"/>
+      <c r="G5" s="227"/>
+      <c r="H5" s="227"/>
+      <c r="I5" s="227"/>
+      <c r="J5" s="227"/>
+      <c r="K5" s="227"/>
+      <c r="L5" s="229"/>
+      <c r="M5" s="229"/>
       <c r="N5" s="102"/>
       <c r="O5" s="89"/>
       <c r="P5" s="102"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="113"/>
       <c r="B6" s="114"/>
       <c r="C6" s="114"/>
@@ -39060,11 +39047,11 @@
       <c r="O6" s="89"/>
       <c r="P6" s="102"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="113"/>
-      <c r="B7" s="202"/>
-      <c r="C7" s="202"/>
-      <c r="D7" s="202"/>
+      <c r="B7" s="218"/>
+      <c r="C7" s="218"/>
+      <c r="D7" s="218"/>
       <c r="E7" s="125" t="s">
         <v>126</v>
       </c>
@@ -39077,8 +39064,8 @@
       <c r="H7" s="125" t="s">
         <v>127</v>
       </c>
-      <c r="I7" s="202"/>
-      <c r="J7" s="202"/>
+      <c r="I7" s="218"/>
+      <c r="J7" s="218"/>
       <c r="K7" s="125" t="s">
         <v>126</v>
       </c>
@@ -39094,11 +39081,11 @@
       <c r="O7" s="89"/>
       <c r="P7" s="102"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="113"/>
-      <c r="B8" s="202"/>
-      <c r="C8" s="202"/>
-      <c r="D8" s="202"/>
+      <c r="B8" s="218"/>
+      <c r="C8" s="218"/>
+      <c r="D8" s="218"/>
       <c r="E8" s="125" t="s">
         <v>1</v>
       </c>
@@ -39111,8 +39098,8 @@
       <c r="H8" s="125" t="s">
         <v>131</v>
       </c>
-      <c r="I8" s="202"/>
-      <c r="J8" s="202"/>
+      <c r="I8" s="218"/>
+      <c r="J8" s="218"/>
       <c r="K8" s="125" t="s">
         <v>1</v>
       </c>
@@ -39128,38 +39115,35 @@
       <c r="O8" s="89"/>
       <c r="P8" s="102"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="113"/>
-      <c r="B9" s="203" t="s">
+      <c r="B9" s="205" t="s">
         <v>75</v>
       </c>
-      <c r="C9" s="203"/>
-      <c r="D9" s="203"/>
-      <c r="E9" s="203"/>
-      <c r="F9" s="203"/>
-      <c r="G9" s="203"/>
-      <c r="H9" s="203" t="s">
+      <c r="C9" s="205"/>
+      <c r="D9" s="205"/>
+      <c r="E9" s="205"/>
+      <c r="F9" s="205"/>
+      <c r="G9" s="205"/>
+      <c r="H9" s="205" t="s">
         <v>132</v>
       </c>
-      <c r="I9" s="203"/>
-      <c r="J9" s="203"/>
-      <c r="K9" s="203"/>
-      <c r="L9" s="203"/>
-      <c r="M9" s="203"/>
-      <c r="N9" s="203"/>
+      <c r="I9" s="205"/>
+      <c r="J9" s="205"/>
+      <c r="K9" s="205"/>
+      <c r="L9" s="205"/>
+      <c r="M9" s="205"/>
+      <c r="N9" s="205"/>
       <c r="O9" s="89"/>
       <c r="P9" s="102"/>
-      <c r="Q9" s="224"/>
-      <c r="R9" s="224"/>
-      <c r="S9" s="224"/>
-    </row>
-    <row r="10" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="113"/>
-      <c r="B10" s="204" t="s">
+      <c r="B10" s="216" t="s">
         <v>133</v>
       </c>
-      <c r="C10" s="204"/>
-      <c r="D10" s="204"/>
+      <c r="C10" s="216"/>
+      <c r="D10" s="216"/>
       <c r="E10" s="126">
         <f>Flujos!H43</f>
         <v>1043317</v>
@@ -39198,31 +39182,31 @@
       </c>
       <c r="O10" s="89"/>
       <c r="P10" s="102"/>
-      <c r="Q10" s="229" t="s">
+      <c r="Q10" s="182" t="s">
         <v>149</v>
       </c>
-      <c r="R10" s="230">
+      <c r="R10" s="183">
         <f>Flujos!C74*Flujos!D74/100</f>
         <v>12.525781012865952</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="113"/>
-      <c r="B11" s="204" t="s">
+      <c r="B11" s="216" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="204"/>
-      <c r="D11" s="204"/>
-      <c r="E11" s="225">
+      <c r="C11" s="216"/>
+      <c r="D11" s="216"/>
+      <c r="E11" s="91">
         <f>Flujos!H6</f>
         <v>0</v>
       </c>
-      <c r="F11" s="226">
+      <c r="F11" s="90">
         <f>Flujos!I6</f>
         <v>0.56565190013</v>
       </c>
-      <c r="G11" s="227"/>
-      <c r="H11" s="228">
+      <c r="G11" s="95"/>
+      <c r="H11" s="92">
         <f>Flujos!J6</f>
         <v>0.54244773027000004</v>
       </c>
@@ -39248,34 +39232,34 @@
       </c>
       <c r="O11" s="89"/>
       <c r="P11" s="102"/>
-      <c r="Q11" s="229" t="s">
+      <c r="Q11" s="182" t="s">
         <v>150</v>
       </c>
-      <c r="R11" s="231">
+      <c r="R11" s="184">
         <f>Flujos!H43*Flujos!D85/100</f>
         <v>130683.60269000266</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="118"/>
-      <c r="B12" s="205" t="s">
+      <c r="B12" s="219" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="205"/>
-      <c r="D12" s="205"/>
-      <c r="E12" s="225">
+      <c r="C12" s="219"/>
+      <c r="D12" s="219"/>
+      <c r="E12" s="91">
         <f>Utilidad!O76</f>
         <v>20429.797500000001</v>
       </c>
-      <c r="F12" s="226">
+      <c r="F12" s="90">
         <f>Flujos!I12</f>
         <v>0.40894900000000001</v>
       </c>
-      <c r="G12" s="227">
+      <c r="G12" s="95">
         <f t="shared" ref="G12:G20" si="0">+E12*F12</f>
         <v>8354.7452578275006</v>
       </c>
-      <c r="H12" s="228">
+      <c r="H12" s="92">
         <f>Flujos!J12</f>
         <v>0.37491300000000005</v>
       </c>
@@ -39287,25 +39271,25 @@
       <c r="N12" s="102"/>
       <c r="O12" s="89"/>
       <c r="P12" s="102"/>
-      <c r="Q12" s="229" t="s">
+      <c r="Q12" s="182" t="s">
         <v>151</v>
       </c>
-      <c r="R12" s="232">
+      <c r="R12" s="185">
         <f>SUM(E12:E20)</f>
         <v>28571.901066920003</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="118"/>
-      <c r="B13" s="205" t="s">
+      <c r="B13" s="219" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="205"/>
-      <c r="D13" s="205"/>
-      <c r="E13" s="225"/>
-      <c r="F13" s="228"/>
-      <c r="G13" s="227"/>
-      <c r="H13" s="228"/>
+      <c r="C13" s="219"/>
+      <c r="D13" s="219"/>
+      <c r="E13" s="91"/>
+      <c r="F13" s="92"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="92"/>
       <c r="I13" s="102"/>
       <c r="J13" s="102"/>
       <c r="K13" s="102"/>
@@ -39314,34 +39298,34 @@
       <c r="N13" s="102"/>
       <c r="O13" s="119"/>
       <c r="P13" s="102"/>
-      <c r="Q13" s="229" t="s">
+      <c r="Q13" s="182" t="s">
         <v>152</v>
       </c>
-      <c r="R13" s="231">
+      <c r="R13" s="184">
         <f>R11+R12</f>
         <v>159255.50375692267</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="118"/>
-      <c r="B14" s="205" t="s">
+      <c r="B14" s="219" t="s">
         <v>143</v>
       </c>
-      <c r="C14" s="205"/>
-      <c r="D14" s="205"/>
-      <c r="E14" s="225">
+      <c r="C14" s="219"/>
+      <c r="D14" s="219"/>
+      <c r="E14" s="91">
         <f>Flujos!H18</f>
         <v>2961.3850000000002</v>
       </c>
-      <c r="F14" s="228">
+      <c r="F14" s="92">
         <f>Flujos!I18</f>
         <v>0.48934499999999997</v>
       </c>
-      <c r="G14" s="227">
+      <c r="G14" s="95">
         <f t="shared" si="0"/>
         <v>1449.138942825</v>
       </c>
-      <c r="H14" s="228">
+      <c r="H14" s="92">
         <f>Flujos!J18</f>
         <v>0.43401600000000001</v>
       </c>
@@ -39353,34 +39337,34 @@
       <c r="N14" s="102"/>
       <c r="O14" s="89"/>
       <c r="P14" s="102"/>
-      <c r="Q14" s="229" t="s">
+      <c r="Q14" s="182" t="s">
         <v>153</v>
       </c>
-      <c r="R14" s="233">
+      <c r="R14" s="186">
         <f>Flujos!H61/R13*100</f>
         <v>43.883569704863078</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="118"/>
-      <c r="B15" s="205" t="s">
+      <c r="B15" s="219" t="s">
         <v>142</v>
       </c>
-      <c r="C15" s="205"/>
-      <c r="D15" s="205"/>
-      <c r="E15" s="225">
+      <c r="C15" s="219"/>
+      <c r="D15" s="219"/>
+      <c r="E15" s="91">
         <f>Utilidad!O85</f>
         <v>451.74641028000002</v>
       </c>
-      <c r="F15" s="228">
+      <c r="F15" s="92">
         <f>Utilidad!P85</f>
         <v>0.40399999999999997</v>
       </c>
-      <c r="G15" s="227">
+      <c r="G15" s="95">
         <f t="shared" si="0"/>
         <v>182.50554975311999</v>
       </c>
-      <c r="H15" s="228">
+      <c r="H15" s="92">
         <f>Flujos!J21</f>
         <v>0.36352800000000002</v>
       </c>
@@ -39392,25 +39376,25 @@
       <c r="N15" s="102"/>
       <c r="O15" s="89"/>
       <c r="P15" s="102"/>
-      <c r="Q15" s="229" t="s">
+      <c r="Q15" s="182" t="s">
         <v>154</v>
       </c>
-      <c r="R15" s="234">
+      <c r="R15" s="187">
         <f>R14*R10/100</f>
         <v>5.496759841859534</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="118"/>
-      <c r="B16" s="205" t="s">
+      <c r="B16" s="219" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="205"/>
-      <c r="D16" s="205"/>
-      <c r="E16" s="225"/>
-      <c r="F16" s="228"/>
-      <c r="G16" s="227"/>
-      <c r="H16" s="228"/>
+      <c r="C16" s="219"/>
+      <c r="D16" s="219"/>
+      <c r="E16" s="91"/>
+      <c r="F16" s="92"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="92"/>
       <c r="I16" s="102"/>
       <c r="J16" s="102"/>
       <c r="K16" s="102"/>
@@ -39419,31 +39403,31 @@
       <c r="N16" s="102"/>
       <c r="O16" s="89"/>
       <c r="P16" s="102"/>
-      <c r="Q16" s="229" t="s">
+      <c r="Q16" s="182" t="s">
         <v>155</v>
       </c>
-      <c r="R16" s="234">
+      <c r="R16" s="187">
         <f>Flujos!J74</f>
         <v>5.489592838340144</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="118"/>
-      <c r="B17" s="205" t="s">
+      <c r="B17" s="219" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="205"/>
-      <c r="D17" s="205"/>
-      <c r="E17" s="225">
+      <c r="C17" s="219"/>
+      <c r="D17" s="219"/>
+      <c r="E17" s="91">
         <f>Flujos!H27</f>
         <v>0</v>
       </c>
-      <c r="F17" s="228">
+      <c r="F17" s="92">
         <f>Flujos!I27</f>
         <v>0.63095048019</v>
       </c>
-      <c r="G17" s="227"/>
-      <c r="H17" s="228">
+      <c r="G17" s="95"/>
+      <c r="H17" s="92">
         <f>Flujos!J27</f>
         <v>0.54504767450000002</v>
       </c>
@@ -39458,24 +39442,24 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="118"/>
-      <c r="B18" s="205" t="s">
+      <c r="B18" s="219" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="205"/>
-      <c r="D18" s="205"/>
-      <c r="E18" s="225">
+      <c r="C18" s="219"/>
+      <c r="D18" s="219"/>
+      <c r="E18" s="91">
         <f>Utilidad!O73</f>
         <v>2654.0249534999998</v>
       </c>
-      <c r="F18" s="228">
+      <c r="F18" s="92">
         <f>Flujos!I9</f>
         <v>0.39713199999999999</v>
       </c>
-      <c r="G18" s="227">
+      <c r="G18" s="95">
         <f t="shared" si="0"/>
         <v>1053.9982378333618</v>
       </c>
-      <c r="H18" s="228">
+      <c r="H18" s="92">
         <f>Flujos!J9</f>
         <v>0.36521099999999995</v>
       </c>
@@ -39490,24 +39474,24 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="118"/>
-      <c r="B19" s="205" t="s">
+      <c r="B19" s="219" t="s">
         <v>144</v>
       </c>
-      <c r="C19" s="205"/>
-      <c r="D19" s="205"/>
-      <c r="E19" s="225">
+      <c r="C19" s="219"/>
+      <c r="D19" s="219"/>
+      <c r="E19" s="91">
         <f>Flujos!H30</f>
         <v>482.97720313999997</v>
       </c>
-      <c r="F19" s="228">
+      <c r="F19" s="92">
         <f>Flujos!I30</f>
         <v>0.42682599999999998</v>
       </c>
-      <c r="G19" s="227">
+      <c r="G19" s="95">
         <f t="shared" si="0"/>
         <v>206.14722770743361</v>
       </c>
-      <c r="H19" s="228">
+      <c r="H19" s="92">
         <f>Flujos!J30</f>
         <v>0.39312900000000001</v>
       </c>
@@ -39522,24 +39506,24 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="118"/>
-      <c r="B20" s="205" t="s">
+      <c r="B20" s="219" t="s">
         <v>145</v>
       </c>
-      <c r="C20" s="205"/>
-      <c r="D20" s="205"/>
-      <c r="E20" s="225">
+      <c r="C20" s="219"/>
+      <c r="D20" s="219"/>
+      <c r="E20" s="91">
         <f>Flujos!H33</f>
         <v>1591.97</v>
       </c>
-      <c r="F20" s="228">
+      <c r="F20" s="92">
         <f>Flujos!I33</f>
         <v>0.47773000000000004</v>
       </c>
-      <c r="G20" s="227">
+      <c r="G20" s="95">
         <f t="shared" si="0"/>
         <v>760.5318281000001</v>
       </c>
-      <c r="H20" s="228">
+      <c r="H20" s="92">
         <f>Flujos!J33</f>
         <v>0.41975999999999997</v>
       </c>
@@ -39554,9 +39538,9 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" s="118"/>
-      <c r="B21" s="205"/>
-      <c r="C21" s="205"/>
-      <c r="D21" s="205"/>
+      <c r="B21" s="219"/>
+      <c r="C21" s="219"/>
+      <c r="D21" s="219"/>
       <c r="E21" s="91"/>
       <c r="F21" s="92"/>
       <c r="G21" s="95"/>
@@ -39572,9 +39556,9 @@
     </row>
     <row r="22" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="118"/>
-      <c r="B22" s="201"/>
-      <c r="C22" s="201"/>
-      <c r="D22" s="201"/>
+      <c r="B22" s="217"/>
+      <c r="C22" s="217"/>
+      <c r="D22" s="217"/>
       <c r="E22" s="98"/>
       <c r="F22" s="128"/>
       <c r="G22" s="129"/>
@@ -39590,11 +39574,11 @@
     </row>
     <row r="23" spans="1:16" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="113"/>
-      <c r="B23" s="222" t="s">
+      <c r="B23" s="214" t="s">
         <v>135</v>
       </c>
-      <c r="C23" s="222"/>
-      <c r="D23" s="222"/>
+      <c r="C23" s="214"/>
+      <c r="D23" s="214"/>
       <c r="E23" s="97">
         <f>SUM(E10:E22)</f>
         <v>1071888.90106692</v>
@@ -39622,33 +39606,33 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" s="113"/>
-      <c r="B24" s="223" t="s">
+      <c r="B24" s="215" t="s">
         <v>136</v>
       </c>
-      <c r="C24" s="223"/>
-      <c r="D24" s="223"/>
-      <c r="E24" s="223"/>
-      <c r="F24" s="223"/>
-      <c r="G24" s="223"/>
-      <c r="H24" s="223" t="s">
+      <c r="C24" s="215"/>
+      <c r="D24" s="215"/>
+      <c r="E24" s="215"/>
+      <c r="F24" s="215"/>
+      <c r="G24" s="215"/>
+      <c r="H24" s="215" t="s">
         <v>137</v>
       </c>
-      <c r="I24" s="223"/>
-      <c r="J24" s="223"/>
-      <c r="K24" s="223"/>
-      <c r="L24" s="223"/>
-      <c r="M24" s="223"/>
+      <c r="I24" s="215"/>
+      <c r="J24" s="215"/>
+      <c r="K24" s="215"/>
+      <c r="L24" s="215"/>
+      <c r="M24" s="215"/>
       <c r="N24" s="102"/>
       <c r="O24" s="89"/>
       <c r="P24" s="102"/>
     </row>
     <row r="25" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="113"/>
-      <c r="B25" s="204" t="s">
+      <c r="B25" s="216" t="s">
         <v>122</v>
       </c>
-      <c r="C25" s="204"/>
-      <c r="D25" s="204"/>
+      <c r="C25" s="216"/>
+      <c r="D25" s="216"/>
       <c r="E25" s="91">
         <f>'Datos Extra'!B1</f>
         <v>93467.25</v>
@@ -39661,11 +39645,11 @@
         <f>+E25*F25</f>
         <v>61413.667473895053</v>
       </c>
-      <c r="H25" s="204" t="s">
+      <c r="H25" s="216" t="s">
         <v>133</v>
       </c>
-      <c r="I25" s="204"/>
-      <c r="J25" s="204"/>
+      <c r="I25" s="216"/>
+      <c r="J25" s="216"/>
       <c r="K25" s="99">
         <f>Flujos!H62</f>
         <v>1002001.9011</v>
@@ -39684,11 +39668,11 @@
     </row>
     <row r="26" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="113"/>
-      <c r="B26" s="214" t="s">
+      <c r="B26" s="206" t="s">
         <v>135</v>
       </c>
-      <c r="C26" s="214"/>
-      <c r="D26" s="214"/>
+      <c r="C26" s="206"/>
+      <c r="D26" s="206"/>
       <c r="E26" s="105">
         <f>SUM(E24:E25)</f>
         <v>93467.25</v>
@@ -39701,11 +39685,11 @@
         <f>SUM(G24:G25)</f>
         <v>61413.667473895053</v>
       </c>
-      <c r="H26" s="214" t="s">
+      <c r="H26" s="206" t="s">
         <v>135</v>
       </c>
-      <c r="I26" s="214"/>
-      <c r="J26" s="214"/>
+      <c r="I26" s="206"/>
+      <c r="J26" s="206"/>
       <c r="K26" s="108">
         <f>K25</f>
         <v>1002001.9011</v>
@@ -39742,20 +39726,20 @@
     </row>
     <row r="28" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="113"/>
-      <c r="B28" s="215" t="s">
+      <c r="B28" s="207" t="s">
         <v>138</v>
       </c>
-      <c r="C28" s="215"/>
-      <c r="D28" s="215"/>
-      <c r="E28" s="215"/>
-      <c r="F28" s="215"/>
-      <c r="G28" s="215"/>
-      <c r="H28" s="215"/>
-      <c r="I28" s="215"/>
-      <c r="J28" s="215"/>
-      <c r="K28" s="215"/>
-      <c r="L28" s="215"/>
-      <c r="M28" s="215"/>
+      <c r="C28" s="207"/>
+      <c r="D28" s="207"/>
+      <c r="E28" s="207"/>
+      <c r="F28" s="207"/>
+      <c r="G28" s="207"/>
+      <c r="H28" s="207"/>
+      <c r="I28" s="207"/>
+      <c r="J28" s="207"/>
+      <c r="K28" s="207"/>
+      <c r="L28" s="207"/>
+      <c r="M28" s="207"/>
       <c r="N28" s="102"/>
       <c r="O28" s="89"/>
       <c r="P28" s="102"/>
@@ -39780,69 +39764,69 @@
     </row>
     <row r="30" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="113"/>
-      <c r="B30" s="216" t="s">
+      <c r="B30" s="208" t="s">
         <v>139</v>
       </c>
-      <c r="C30" s="217"/>
-      <c r="D30" s="218"/>
+      <c r="C30" s="209"/>
+      <c r="D30" s="210"/>
       <c r="E30" s="102"/>
       <c r="F30" s="102"/>
-      <c r="G30" s="219" t="s">
+      <c r="G30" s="211" t="s">
         <v>140</v>
       </c>
-      <c r="H30" s="220"/>
-      <c r="I30" s="221"/>
+      <c r="H30" s="212"/>
+      <c r="I30" s="213"/>
       <c r="J30" s="102"/>
-      <c r="K30" s="216" t="s">
+      <c r="K30" s="208" t="s">
         <v>141</v>
       </c>
-      <c r="L30" s="217"/>
-      <c r="M30" s="218"/>
+      <c r="L30" s="209"/>
+      <c r="M30" s="210"/>
       <c r="N30" s="102"/>
       <c r="O30" s="89"/>
       <c r="P30" s="102"/>
     </row>
     <row r="31" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="131"/>
-      <c r="B31" s="206">
+      <c r="B31" s="197">
         <f>Flujos!J74/100</f>
         <v>5.4895928383401439E-2</v>
       </c>
-      <c r="C31" s="206"/>
-      <c r="D31" s="206"/>
+      <c r="C31" s="197"/>
+      <c r="D31" s="197"/>
       <c r="E31" s="102"/>
       <c r="F31" s="102"/>
-      <c r="G31" s="207">
+      <c r="G31" s="198">
         <f>Utilidad!I94</f>
         <v>0.33177196735015535</v>
       </c>
-      <c r="H31" s="207"/>
-      <c r="I31" s="207"/>
+      <c r="H31" s="198"/>
+      <c r="I31" s="198"/>
       <c r="J31" s="102"/>
-      <c r="K31" s="208">
+      <c r="K31" s="199">
         <f>Utilidad!I104</f>
         <v>0.68979989099589545</v>
       </c>
-      <c r="L31" s="209"/>
-      <c r="M31" s="210"/>
+      <c r="L31" s="200"/>
+      <c r="M31" s="201"/>
       <c r="N31" s="102"/>
       <c r="O31" s="89"/>
       <c r="P31" s="102"/>
     </row>
     <row r="32" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14"/>
-      <c r="B32" s="207"/>
-      <c r="C32" s="207"/>
-      <c r="D32" s="207"/>
+      <c r="B32" s="198"/>
+      <c r="C32" s="198"/>
+      <c r="D32" s="198"/>
       <c r="E32" s="102"/>
       <c r="F32" s="102"/>
-      <c r="G32" s="207"/>
-      <c r="H32" s="207"/>
-      <c r="I32" s="207"/>
+      <c r="G32" s="198"/>
+      <c r="H32" s="198"/>
+      <c r="I32" s="198"/>
       <c r="J32" s="102"/>
-      <c r="K32" s="211"/>
-      <c r="L32" s="212"/>
-      <c r="M32" s="213"/>
+      <c r="K32" s="202"/>
+      <c r="L32" s="203"/>
+      <c r="M32" s="204"/>
       <c r="O32" s="89"/>
     </row>
     <row r="33" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -39920,6 +39904,26 @@
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="B2:C5"/>
+    <mergeCell ref="D2:M3"/>
+    <mergeCell ref="D4:I5"/>
+    <mergeCell ref="J4:K5"/>
+    <mergeCell ref="L4:M5"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B7:D8"/>
+    <mergeCell ref="I7:J8"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
     <mergeCell ref="B31:D32"/>
     <mergeCell ref="G31:I32"/>
     <mergeCell ref="K31:M32"/>
@@ -39936,26 +39940,6 @@
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="H25:J25"/>
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B7:D8"/>
-    <mergeCell ref="I7:J8"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B2:C5"/>
-    <mergeCell ref="D2:M3"/>
-    <mergeCell ref="D4:I5"/>
-    <mergeCell ref="J4:K5"/>
-    <mergeCell ref="L4:M5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup scale="85" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
